--- a/artfynd/A 36051-2024 artfynd.xlsx
+++ b/artfynd/A 36051-2024 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>119796487</v>
       </c>
       <c r="B4" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
